--- a/Hoe lang moet ik nog wachten/Hoe lang moet ik nog wachten.xlsx
+++ b/Hoe lang moet ik nog wachten/Hoe lang moet ik nog wachten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henkj\Documents\GitHub\RandomRepository\Hoe lang moet ik nog wachten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8A76DD-E3B1-42EC-8197-E23DF77B24ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72F56F0-FCA4-41B7-8CC4-4E5C57F3AAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -649,7 +649,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>147221</xdr:colOff>
+      <xdr:colOff>147220</xdr:colOff>
       <xdr:row>102</xdr:row>
       <xdr:rowOff>20566</xdr:rowOff>
     </xdr:to>
@@ -680,7 +680,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="971"/>
-          <a:ext cx="5976521" cy="16535945"/>
+          <a:ext cx="5976520" cy="16535945"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1081,7 +1081,7 @@
         <v>46135.640972222223</v>
       </c>
       <c r="H2" s="10">
-        <f>((G2-$K$2)/$K$1-F2)</f>
+        <f t="shared" ref="H2:H19" si="1">((G2-$K$2)/$K$1-F2)</f>
         <v>-0.16923316454477799</v>
       </c>
       <c r="J2" t="s">
@@ -1131,7 +1131,7 @@
         <v>46135.642361111109</v>
       </c>
       <c r="H3" s="10">
-        <f>((G3-$K$2)/$K$1-F3)</f>
+        <f t="shared" si="1"/>
         <v>-0.13859076922688018</v>
       </c>
     </row>
@@ -1155,11 +1155,11 @@
         <v>161</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" ref="G4:G12" si="1">DATE(A4,B4,C4)+TIME(D4,E4,0)</f>
+        <f t="shared" ref="G4:G12" si="2">DATE(A4,B4,C4)+TIME(D4,E4,0)</f>
         <v>46135.644444444442</v>
       </c>
       <c r="H4" s="10">
-        <f>((G4-$K$2)/$K$1-F4)</f>
+        <f t="shared" si="1"/>
         <v>0.40737283168826366</v>
       </c>
       <c r="J4" t="s">
@@ -1190,11 +1190,11 @@
         <v>172</v>
       </c>
       <c r="G5" s="4">
+        <f t="shared" si="2"/>
+        <v>46135.649305555555</v>
+      </c>
+      <c r="H5" s="10">
         <f t="shared" si="1"/>
-        <v>46135.649305555555</v>
-      </c>
-      <c r="H5" s="10">
-        <f>((G5-$K$2)/$K$1-F5)</f>
         <v>1.4621239115825801E-2</v>
       </c>
       <c r="J5" t="s">
@@ -1226,11 +1226,11 @@
         <v>183</v>
       </c>
       <c r="G6" s="4">
+        <f t="shared" si="2"/>
+        <v>46135.654166666667</v>
+      </c>
+      <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>46135.654166666667</v>
-      </c>
-      <c r="H6" s="10">
-        <f>((G6-$K$2)/$K$1-F6)</f>
         <v>-0.37813035345661206</v>
       </c>
       <c r="J6" t="s">
@@ -1263,11 +1263,11 @@
         <v>187</v>
       </c>
       <c r="G7" s="4">
+        <f t="shared" si="2"/>
+        <v>46135.65625</v>
+      </c>
+      <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>46135.65625</v>
-      </c>
-      <c r="H7" s="10">
-        <f>((G7-$K$2)/$K$1-F7)</f>
         <v>0.16783324745853179</v>
       </c>
     </row>
@@ -1291,11 +1291,11 @@
         <v>196</v>
       </c>
       <c r="G8" s="4">
+        <f t="shared" si="2"/>
+        <v>46135.660416666666</v>
+      </c>
+      <c r="H8" s="10">
         <f t="shared" si="1"/>
-        <v>46135.660416666666</v>
-      </c>
-      <c r="H8" s="10">
-        <f>((G8-$K$2)/$K$1-F8)</f>
         <v>0.25976044928884789</v>
       </c>
       <c r="J8" s="8" t="s">
@@ -1322,11 +1322,11 @@
         <v>204</v>
       </c>
       <c r="G9" s="4">
+        <f t="shared" si="2"/>
+        <v>46135.663888888892</v>
+      </c>
+      <c r="H9" s="10">
         <f t="shared" si="1"/>
-        <v>46135.663888888892</v>
-      </c>
-      <c r="H9" s="10">
-        <f>((G9-$K$2)/$K$1-F9)</f>
         <v>-0.16363353860148777</v>
       </c>
       <c r="J9" s="8" t="s">
@@ -1347,11 +1347,11 @@
         <v>15</v>
       </c>
       <c r="G10" s="4">
+        <f t="shared" si="2"/>
+        <v>46135.625</v>
+      </c>
+      <c r="H10" s="10">
         <f t="shared" si="1"/>
-        <v>46135.625</v>
-      </c>
-      <c r="H10" s="10">
-        <f>((G10-$K$2)/$K$1-F10)</f>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1369,11 +1369,11 @@
         <v>15</v>
       </c>
       <c r="G11" s="4">
+        <f t="shared" si="2"/>
+        <v>46135.625</v>
+      </c>
+      <c r="H11" s="10">
         <f t="shared" si="1"/>
-        <v>46135.625</v>
-      </c>
-      <c r="H11" s="10">
-        <f>((G11-$K$2)/$K$1-F11)</f>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1391,11 +1391,11 @@
         <v>15</v>
       </c>
       <c r="G12" s="4">
+        <f t="shared" si="2"/>
+        <v>46135.625</v>
+      </c>
+      <c r="H12" s="10">
         <f t="shared" si="1"/>
-        <v>46135.625</v>
-      </c>
-      <c r="H12" s="10">
-        <f>((G12-$K$2)/$K$1-F12)</f>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1413,11 +1413,11 @@
         <v>15</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" ref="G13" si="2">DATE(A13,B13,C13)+TIME(D13,E13,0)</f>
+        <f t="shared" ref="G13" si="3">DATE(A13,B13,C13)+TIME(D13,E13,0)</f>
         <v>46135.625</v>
       </c>
       <c r="H13" s="10">
-        <f>((G13-$K$2)/$K$1-F13)</f>
+        <f t="shared" si="1"/>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1435,11 +1435,11 @@
         <v>15</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" ref="G14:G16" si="3">DATE(A14,B14,C14)+TIME(D14,E14,0)</f>
+        <f t="shared" ref="G14:G16" si="4">DATE(A14,B14,C14)+TIME(D14,E14,0)</f>
         <v>46135.625</v>
       </c>
       <c r="H14" s="10">
-        <f>((G14-$K$2)/$K$1-F14)</f>
+        <f t="shared" si="1"/>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1457,11 +1457,11 @@
         <v>15</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>46135.625</v>
       </c>
       <c r="H15" s="10">
-        <f>((G15-$K$2)/$K$1-F15)</f>
+        <f t="shared" si="1"/>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1479,11 +1479,11 @@
         <v>15</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>46135.625</v>
       </c>
       <c r="H16" s="10">
-        <f>((G16-$K$2)/$K$1-F16)</f>
+        <f t="shared" si="1"/>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1501,11 +1501,11 @@
         <v>15</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" ref="G17:G19" si="4">DATE(A17,B17,C17)+TIME(D17,E17,0)</f>
+        <f t="shared" ref="G17:G19" si="5">DATE(A17,B17,C17)+TIME(D17,E17,0)</f>
         <v>46135.625</v>
       </c>
       <c r="H17" s="10">
-        <f>((G17-$K$2)/$K$1-F17)</f>
+        <f t="shared" si="1"/>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1523,11 +1523,11 @@
         <v>15</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>46135.625</v>
       </c>
       <c r="H18" s="10">
-        <f>((G18-$K$2)/$K$1-F18)</f>
+        <f t="shared" si="1"/>
         <v>118.97837921785464</v>
       </c>
     </row>
@@ -1545,11 +1545,11 @@
         <v>15</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>46135.625</v>
       </c>
       <c r="H19" s="10">
-        <f>((G19-$K$2)/$K$1-F19)</f>
+        <f t="shared" si="1"/>
         <v>118.97837921785464</v>
       </c>
     </row>

--- a/Hoe lang moet ik nog wachten/Hoe lang moet ik nog wachten.xlsx
+++ b/Hoe lang moet ik nog wachten/Hoe lang moet ik nog wachten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henkj\Documents\GitHub\RandomRepository\Hoe lang moet ik nog wachten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72F56F0-FCA4-41B7-8CC4-4E5C57F3AAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448FED51-5A03-4F9A-A557-32956344054E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -391,58 +391,58 @@
                 <c:formatCode>dd\-mm\-yyyy" "hh":"mm</c:formatCode>
                 <c:ptCount val="986"/>
                 <c:pt idx="0">
-                  <c:v>46135.640972222223</c:v>
+                  <c:v>46131.893055555556</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46135.642361111109</c:v>
+                  <c:v>46131.894444444442</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46135.644444444442</c:v>
+                  <c:v>46131.895833333336</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46135.649305555555</c:v>
+                  <c:v>46131.899305555555</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46135.654166666667</c:v>
+                  <c:v>46131.900694444441</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46135.65625</c:v>
+                  <c:v>46131.902777777781</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46135.660416666666</c:v>
+                  <c:v>46131.904166666667</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46135.663888888892</c:v>
+                  <c:v>46131.90625</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.906944444447</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.908333333333</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.909722222219</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.911111111112</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.914583333331</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.875</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.875</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.875</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46135.625</c:v>
+                  <c:v>46131.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -454,28 +454,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="986"/>
                 <c:pt idx="0">
-                  <c:v>154</c:v>
+                  <c:v>31591</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>157</c:v>
+                  <c:v>31646</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>161</c:v>
+                  <c:v>31691</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>172</c:v>
+                  <c:v>31839</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>183</c:v>
+                  <c:v>31901</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>187</c:v>
+                  <c:v>31990</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>196</c:v>
+                  <c:v>32045</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>204</c:v>
+                  <c:v>32112</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32156</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32223</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>32273</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>32384</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32487</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1040,18 +1055,18 @@
       </c>
       <c r="K1">
         <f>SLOPE(G:G,F:F)</f>
-        <v>4.5828200921557553E-4</v>
+        <v>2.3609957188638396E-5</v>
       </c>
       <c r="M1" s="12">
         <f>3600*K1*24</f>
-        <v>39.595565596225725</v>
+        <v>2.0399003010983572</v>
       </c>
       <c r="N1" t="s">
         <v>5</v>
       </c>
       <c r="O1" s="11">
         <f>1/M1</f>
-        <v>2.5255353344297741E-2</v>
+        <v>0.4902200364701958</v>
       </c>
       <c r="P1" t="s">
         <v>18</v>
@@ -1065,43 +1080,43 @@
         <v>4</v>
       </c>
       <c r="C2" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
-        <v>154</v>
+        <v>31591</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:G3" si="0">DATE(A2,B2,C2)+TIME(D2,E2,0)</f>
-        <v>46135.640972222223</v>
+        <v>46131.893055555556</v>
       </c>
       <c r="H2" s="10">
         <f t="shared" ref="H2:H19" si="1">((G2-$K$2)/$K$1-F2)</f>
-        <v>-0.16923316454477799</v>
+        <v>-12.985694606326433</v>
       </c>
       <c r="J2" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="1">
         <f>INTERCEPT(G:G,F:F)</f>
-        <v>46135.570474349319</v>
+        <v>46131.147499989704</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="12">
         <f>M1/60</f>
-        <v>0.65992609327042873</v>
+        <v>3.3998338351639283E-2</v>
       </c>
       <c r="N2" t="s">
         <v>6</v>
       </c>
       <c r="O2" s="11">
         <f>1/M2</f>
-        <v>1.5153212006578647</v>
+        <v>29.413202188211748</v>
       </c>
       <c r="P2" t="s">
         <v>7</v>
@@ -1115,24 +1130,24 @@
         <v>4</v>
       </c>
       <c r="C3" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
-        <v>157</v>
+        <v>31646</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="0"/>
-        <v>46135.642361111109</v>
+        <v>46131.894444444442</v>
       </c>
       <c r="H3" s="10">
         <f t="shared" si="1"/>
-        <v>-0.13859076922688018</v>
+        <v>-9.1592903463242692</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -1143,30 +1158,30 @@
         <v>4</v>
       </c>
       <c r="C4" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3">
-        <v>161</v>
+        <v>31691</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" ref="G4:G12" si="2">DATE(A4,B4,C4)+TIME(D4,E4,0)</f>
-        <v>46135.644444444442</v>
+        <v>46131.895833333336</v>
       </c>
       <c r="H4" s="10">
         <f t="shared" si="1"/>
-        <v>0.40737283168826366</v>
+        <v>4.6671142218510795</v>
       </c>
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="7">
-        <v>321</v>
+        <v>36131</v>
       </c>
       <c r="L4" s="7"/>
     </row>
@@ -1178,31 +1193,31 @@
         <v>4</v>
       </c>
       <c r="C5" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E5" s="3">
         <v>35</v>
       </c>
       <c r="F5" s="3">
-        <v>172</v>
+        <v>31839</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="2"/>
-        <v>46135.649305555555</v>
+        <v>46131.899305555555</v>
       </c>
       <c r="H5" s="10">
         <f t="shared" si="1"/>
-        <v>1.4621239115825801E-2</v>
+        <v>3.7331250259449007</v>
       </c>
       <c r="J5" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="1">
         <f>K2+K1*K4</f>
-        <v>46135.717582874277</v>
+        <v>46132.000551352889</v>
       </c>
       <c r="L5" s="1"/>
     </row>
@@ -1214,31 +1229,31 @@
         <v>4</v>
       </c>
       <c r="C6" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F6" s="3">
-        <v>183</v>
+        <v>31901</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="2"/>
-        <v>46135.654166666667</v>
+        <v>46131.900694444441</v>
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>-0.37813035345661206</v>
+        <v>0.55952928594706464</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6" s="2">
         <f>CORREL(G:G,F:F)</f>
-        <v>0.99990159209756047</v>
+        <v>0.99851898442333265</v>
       </c>
       <c r="L6" s="2"/>
       <c r="O6" s="13"/>
@@ -1251,24 +1266,24 @@
         <v>4</v>
       </c>
       <c r="C7" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3">
-        <v>187</v>
+        <v>31990</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="2"/>
-        <v>46135.65625</v>
+        <v>46131.902777777781</v>
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>0.16783324745853179</v>
+        <v>-0.20086386179173132</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
@@ -1279,24 +1294,24 @@
         <v>4</v>
       </c>
       <c r="C8" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3">
-        <v>196</v>
+        <v>32045</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="2"/>
-        <v>46135.660416666666</v>
+        <v>46131.904166666667</v>
       </c>
       <c r="H8" s="10">
         <f t="shared" si="1"/>
-        <v>0.25976044928884789</v>
+        <v>3.6255403982104326</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>15</v>
@@ -1310,24 +1325,24 @@
         <v>4</v>
       </c>
       <c r="C9" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F9" s="3">
-        <v>204</v>
+        <v>32112</v>
       </c>
       <c r="G9" s="4">
         <f t="shared" si="2"/>
-        <v>46135.663888888892</v>
+        <v>46131.90625</v>
       </c>
       <c r="H9" s="10">
         <f t="shared" si="1"/>
-        <v>-0.16363353860148777</v>
+        <v>24.86514694230209</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
@@ -1341,18 +1356,24 @@
         <v>4</v>
       </c>
       <c r="C10" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46</v>
+      </c>
+      <c r="F10" s="3">
+        <v>32156</v>
       </c>
       <c r="G10" s="4">
         <f t="shared" si="2"/>
-        <v>46135.625</v>
+        <v>46131.906944444447</v>
       </c>
       <c r="H10" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>10.278349226391583</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
@@ -1363,18 +1384,24 @@
         <v>4</v>
       </c>
       <c r="C11" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E11" s="3">
+        <v>48</v>
+      </c>
+      <c r="F11" s="3">
+        <v>32223</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="2"/>
-        <v>46135.625</v>
+        <v>46131.908333333333</v>
       </c>
       <c r="H11" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>2.1047534863937472</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -1385,18 +1412,24 @@
         <v>4</v>
       </c>
       <c r="C12" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E12" s="3">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3">
+        <v>32273</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="2"/>
-        <v>46135.625</v>
+        <v>46131.909722222219</v>
       </c>
       <c r="H12" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>10.931157746395911</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -1407,18 +1440,24 @@
         <v>4</v>
       </c>
       <c r="C13" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E13" s="3">
+        <v>52</v>
+      </c>
+      <c r="F13" s="3">
+        <v>32384</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" ref="G13" si="3">DATE(A13,B13,C13)+TIME(D13,E13,0)</f>
-        <v>46135.625</v>
+        <v>46131.911111111112</v>
       </c>
       <c r="H13" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>-41.24243768542874</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
@@ -1429,18 +1468,24 @@
         <v>4</v>
       </c>
       <c r="C14" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E14" s="3">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3">
+        <v>32487</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" ref="G14:G16" si="4">DATE(A14,B14,C14)+TIME(D14,E14,0)</f>
-        <v>46135.625</v>
+        <v>46131.914583333331</v>
       </c>
       <c r="H14" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>2.823573118665081</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
@@ -1451,18 +1496,18 @@
         <v>4</v>
       </c>
       <c r="C15" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="4"/>
-        <v>46135.625</v>
+        <v>46131.875</v>
       </c>
       <c r="H15" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>30813.271048472772</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
@@ -1473,18 +1518,18 @@
         <v>4</v>
       </c>
       <c r="C16" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D16" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="4"/>
-        <v>46135.625</v>
+        <v>46131.875</v>
       </c>
       <c r="H16" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>30813.271048472772</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -1495,18 +1540,18 @@
         <v>4</v>
       </c>
       <c r="C17" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D17" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" ref="G17:G19" si="5">DATE(A17,B17,C17)+TIME(D17,E17,0)</f>
-        <v>46135.625</v>
+        <v>46131.875</v>
       </c>
       <c r="H17" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>30813.271048472772</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -1517,18 +1562,18 @@
         <v>4</v>
       </c>
       <c r="C18" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="5"/>
-        <v>46135.625</v>
+        <v>46131.875</v>
       </c>
       <c r="H18" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>30813.271048472772</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -1539,18 +1584,18 @@
         <v>4</v>
       </c>
       <c r="C19" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D19" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="5"/>
-        <v>46135.625</v>
+        <v>46131.875</v>
       </c>
       <c r="H19" s="10">
         <f t="shared" si="1"/>
-        <v>118.97837921785464</v>
+        <v>30813.271048472772</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">

--- a/Hoe lang moet ik nog wachten/Hoe lang moet ik nog wachten.xlsx
+++ b/Hoe lang moet ik nog wachten/Hoe lang moet ik nog wachten.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henkj\Documents\GitHub\RandomRepository\Hoe lang moet ik nog wachten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asmpac-my.sharepoint.com/personal/henkjan_van_der_pol_asmpt_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448FED51-5A03-4F9A-A557-32956344054E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{5A178654-5749-43B0-9A7A-2F640464C381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A06DAA49-E030-4F55-A0D2-7C11E2178751}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="2" r:id="rId1"/>
-    <sheet name="Gebruiksaanwijzing" sheetId="3" r:id="rId2"/>
+    <sheet name="Prediction" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Slope</t>
   </si>
@@ -91,17 +90,22 @@
   </si>
   <si>
     <t>Hz</t>
+  </si>
+  <si>
+    <t>Sec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy&quot; &quot;hh&quot;:&quot;mm"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="00"/>
+    <numFmt numFmtId="167" formatCode="dd\-mm\-yyyy&quot; &quot;hh&quot;:&quot;mm&quot;:&quot;ss"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -294,20 +298,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -321,6 +319,24 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -362,7 +378,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -384,113 +400,121 @@
             <c:symbol val="square"/>
             <c:size val="7"/>
           </c:marker>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Data!$G$2:$G$987</c:f>
+              <c:f>Prediction!$H$2:$H$987</c:f>
               <c:numCache>
-                <c:formatCode>dd\-mm\-yyyy" "hh":"mm</c:formatCode>
+                <c:formatCode>dd\-mm\-yyyy" "hh":"mm":"ss</c:formatCode>
                 <c:ptCount val="986"/>
                 <c:pt idx="0">
-                  <c:v>46131.893055555556</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46131.894444444442</c:v>
+                  <c:v>46190.891250000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46131.895833333336</c:v>
+                  <c:v>46190.891377314816</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46131.899305555555</c:v>
+                  <c:v>46190.891527777778</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46131.900694444441</c:v>
+                  <c:v>46190.89166666667</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46131.902777777781</c:v>
+                  <c:v>46190.892777777779</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46131.904166666667</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46131.90625</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46131.906944444447</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46131.908333333333</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46131.909722222219</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46131.911111111112</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46131.914583333331</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46131.875</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46131.875</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46131.875</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46131.875</c:v>
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46131.875</c:v>
+                  <c:v>46190.891099537039</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46190.891099537039</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190.891099537039</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46190.891099537039</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46190.891099537039</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46190.891099537039</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46190.891099537039</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46190.891099537039</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46190.891099537039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Data!$F$2:$F$987</c:f>
+              <c:f>Prediction!$G$2:$G$987</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="986"/>
                 <c:pt idx="0">
-                  <c:v>31591</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31646</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>31691</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31839</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>31901</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>31990</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>32045</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>32112</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>32156</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>32223</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>32273</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>32384</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>32487</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -529,7 +553,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -625,7 +649,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
-    <xdr:pos x="5219738" y="1514558"/>
+    <xdr:pos x="7940078" y="455378"/>
     <xdr:ext cx="4781880" cy="2631960"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -650,60 +674,6 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>971</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>147220</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>20566</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F0AA0CE-A854-399A-B65D-3C27151FC93D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="971"/>
-          <a:ext cx="5976520" cy="16535945"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1004,606 +974,875 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.53125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="2.86328125" customWidth="1"/>
-    <col min="10" max="10" width="10.46484375" customWidth="1"/>
-    <col min="11" max="11" width="16.1328125" customWidth="1"/>
-    <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="8.796875" style="12" customWidth="1"/>
-    <col min="14" max="14" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.796875" style="11" customWidth="1"/>
-    <col min="17" max="17" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="7.21875" style="3" customWidth="1"/>
+    <col min="5" max="6" width="7.21875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="8" customWidth="1"/>
+    <col min="10" max="10" width="2.88671875" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" style="10" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.77734375" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="I1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="10">
+        <f>3600*L2*24</f>
+        <v>13.225806452814608</v>
+      </c>
+      <c r="O1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="9">
+        <f>1/N1</f>
+        <v>7.5609756090691024E-2</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="3">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3">
+        <v>21</v>
+      </c>
+      <c r="E2" s="15">
+        <v>23</v>
+      </c>
+      <c r="F2" s="15">
+        <v>11</v>
+      </c>
+      <c r="G2" s="13">
+        <v>5</v>
+      </c>
+      <c r="H2" s="17">
+        <f>DATE(A2,B2,C2)+TIME(D2,E2,F2)</f>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I2" s="8">
+        <f>((H2-$L$3)/$L$2-G2)</f>
+        <v>0.12276424099597971</v>
+      </c>
+      <c r="K2" t="s">
         <v>0</v>
       </c>
-      <c r="K1">
-        <f>SLOPE(G:G,F:F)</f>
-        <v>2.3609957188638396E-5</v>
-      </c>
-      <c r="M1" s="12">
-        <f>3600*K1*24</f>
-        <v>2.0399003010983572</v>
-      </c>
-      <c r="N1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="11">
-        <f>1/M1</f>
-        <v>0.4902200364701958</v>
-      </c>
-      <c r="P1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <v>2026</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="L2">
+        <f>SLOPE(H:H,G:G)</f>
+        <v>1.5307646357424316E-4</v>
+      </c>
+      <c r="N2" s="10">
+        <f>N1/60</f>
+        <v>0.22043010754691011</v>
+      </c>
+      <c r="O2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="9">
+        <f>1/N2</f>
+        <v>4.5365853654414616</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3">
+        <v>21</v>
+      </c>
+      <c r="E3" s="15">
+        <v>23</v>
+      </c>
+      <c r="F3" s="15">
+        <v>24</v>
+      </c>
+      <c r="G3" s="13">
+        <v>6</v>
+      </c>
+      <c r="H3" s="17">
+        <f t="shared" ref="H3:H27" si="0">DATE(A3,B3,C3)+TIME(D3,E3,F3)</f>
+        <v>46190.891250000001</v>
+      </c>
+      <c r="I3" s="8">
+        <f>((H3-$L$3)/$L$2-G3)</f>
+        <v>0.1056910622882512</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <f>INTERCEPT(H:H,G:G)</f>
+        <v>46190.890315362405</v>
+      </c>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3">
+        <v>21</v>
+      </c>
+      <c r="E4" s="15">
+        <v>23</v>
+      </c>
+      <c r="F4" s="15">
+        <v>35</v>
+      </c>
+      <c r="G4" s="13">
+        <v>7</v>
+      </c>
+      <c r="H4" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891377314816</v>
+      </c>
+      <c r="I4" s="8">
+        <f>((H4-$L$3)/$L$2-G4)</f>
+        <v>-6.2601616418706207E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="3">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3">
+        <v>21</v>
+      </c>
+      <c r="E5" s="15">
+        <v>23</v>
+      </c>
+      <c r="F5" s="15">
+        <v>48</v>
+      </c>
+      <c r="G5" s="13">
+        <v>8</v>
+      </c>
+      <c r="H5" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891527777778</v>
+      </c>
+      <c r="I5" s="8">
+        <f>((H5-$L$3)/$L$2-G5)</f>
+        <v>-7.9674795126434717E-2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1500</v>
+      </c>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3">
+        <v>21</v>
+      </c>
+      <c r="E6" s="15">
+        <v>24</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13">
+        <v>9</v>
+      </c>
+      <c r="H6" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.89166666667</v>
+      </c>
+      <c r="I6" s="8">
+        <f>((H6-$L$3)/$L$2-G6)</f>
+        <v>-0.17235770006801587</v>
+      </c>
+      <c r="K6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <f>L3+L2*L5</f>
+        <v>46191.119930057765</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="P6" s="11"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="3">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3">
+        <v>21</v>
+      </c>
+      <c r="E7" s="15">
+        <v>25</v>
+      </c>
+      <c r="F7" s="15">
+        <v>36</v>
+      </c>
+      <c r="G7" s="13">
+        <v>16</v>
+      </c>
+      <c r="H7" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.892777777779</v>
+      </c>
+      <c r="I7" s="8">
+        <f>((H7-$L$3)/$L$2-G7)</f>
+        <v>8.6178870273240449E-2</v>
+      </c>
+      <c r="K7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3">
-        <v>19</v>
-      </c>
-      <c r="D2" s="3">
-        <v>21</v>
-      </c>
-      <c r="E2" s="3">
-        <v>26</v>
-      </c>
-      <c r="F2" s="3">
-        <v>31591</v>
-      </c>
-      <c r="G2" s="4">
-        <f t="shared" ref="G2:G3" si="0">DATE(A2,B2,C2)+TIME(D2,E2,0)</f>
-        <v>46131.893055555556</v>
-      </c>
-      <c r="H2" s="10">
-        <f t="shared" ref="H2:H19" si="1">((G2-$K$2)/$K$1-F2)</f>
-        <v>-12.985694606326433</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1">
-        <f>INTERCEPT(G:G,F:F)</f>
-        <v>46131.147499989704</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="12">
-        <f>M1/60</f>
-        <v>3.3998338351639283E-2</v>
-      </c>
-      <c r="N2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="11">
-        <f>1/M2</f>
-        <v>29.413202188211748</v>
-      </c>
-      <c r="P2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="3">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3">
-        <v>28</v>
-      </c>
-      <c r="F3" s="3">
-        <v>31646</v>
-      </c>
-      <c r="G3" s="4">
-        <f t="shared" si="0"/>
-        <v>46131.894444444442</v>
-      </c>
-      <c r="H3" s="10">
-        <f t="shared" si="1"/>
-        <v>-9.1592903463242692</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="3">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3">
-        <v>21</v>
-      </c>
-      <c r="E4" s="3">
-        <v>30</v>
-      </c>
-      <c r="F4" s="3">
-        <v>31691</v>
-      </c>
-      <c r="G4" s="4">
-        <f t="shared" ref="G4:G12" si="2">DATE(A4,B4,C4)+TIME(D4,E4,0)</f>
-        <v>46131.895833333336</v>
-      </c>
-      <c r="H4" s="10">
-        <f t="shared" si="1"/>
-        <v>4.6671142218510795</v>
-      </c>
-      <c r="J4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" s="7">
-        <v>36131</v>
-      </c>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="3">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3">
-        <v>35</v>
-      </c>
-      <c r="F5" s="3">
-        <v>31839</v>
-      </c>
-      <c r="G5" s="4">
-        <f t="shared" si="2"/>
-        <v>46131.899305555555</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="1"/>
-        <v>3.7331250259449007</v>
-      </c>
-      <c r="J5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K5" s="1">
-        <f>K2+K1*K4</f>
-        <v>46132.000551352889</v>
-      </c>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="3">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3">
-        <v>19</v>
-      </c>
-      <c r="D6" s="3">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3">
-        <v>37</v>
-      </c>
-      <c r="F6" s="3">
-        <v>31901</v>
-      </c>
-      <c r="G6" s="4">
-        <f t="shared" si="2"/>
-        <v>46131.900694444441</v>
-      </c>
-      <c r="H6" s="10">
-        <f t="shared" si="1"/>
-        <v>0.55952928594706464</v>
-      </c>
-      <c r="J6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K6" s="2">
-        <f>CORREL(G:G,F:F)</f>
-        <v>0.99851898442333265</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="O6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
-        <v>2026</v>
-      </c>
-      <c r="B7" s="3">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3">
-        <v>40</v>
-      </c>
-      <c r="F7" s="3">
-        <v>31990</v>
-      </c>
-      <c r="G7" s="4">
-        <f t="shared" si="2"/>
-        <v>46131.902777777781</v>
-      </c>
-      <c r="H7" s="10">
-        <f t="shared" si="1"/>
-        <v>-0.20086386179173132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L7" s="2">
+        <f>CORREL(H:H,G:G)</f>
+        <v>0.99952522433641244</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="3">
         <v>2026</v>
       </c>
       <c r="B8" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3">
         <v>21</v>
       </c>
-      <c r="E8" s="3">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3">
-        <v>32045</v>
-      </c>
-      <c r="G8" s="4">
-        <f t="shared" si="2"/>
-        <v>46131.904166666667</v>
-      </c>
-      <c r="H8" s="10">
-        <f t="shared" si="1"/>
-        <v>3.6255403982104326</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="E8" s="15">
+        <v>23</v>
+      </c>
+      <c r="F8" s="15">
+        <v>11</v>
+      </c>
+      <c r="H8" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I8" s="8">
+        <f>((H8-$L$3)/$L$2-G8)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="3">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>17</v>
+      </c>
+      <c r="D9" s="3">
+        <v>21</v>
+      </c>
+      <c r="E9" s="15">
+        <v>23</v>
+      </c>
+      <c r="F9" s="15">
+        <v>11</v>
+      </c>
+      <c r="H9" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I9" s="8">
+        <f>((H9-$L$3)/$L$2-G9)</f>
+        <v>5.1227642409959797</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>2026</v>
-      </c>
-      <c r="B9" s="3">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3">
-        <v>21</v>
-      </c>
-      <c r="E9" s="3">
-        <v>45</v>
-      </c>
-      <c r="F9" s="3">
-        <v>32112</v>
-      </c>
-      <c r="G9" s="4">
-        <f t="shared" si="2"/>
-        <v>46131.90625</v>
-      </c>
-      <c r="H9" s="10">
-        <f t="shared" si="1"/>
-        <v>24.86514694230209</v>
-      </c>
-      <c r="J9" s="8" t="s">
+    <row r="10" spans="1:17">
+      <c r="A10" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="3">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3">
+        <v>21</v>
+      </c>
+      <c r="E10" s="15">
+        <v>23</v>
+      </c>
+      <c r="F10" s="15">
+        <v>11</v>
+      </c>
+      <c r="H10" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I10" s="8">
+        <f>((H10-$L$3)/$L$2-G10)</f>
+        <v>5.1227642409959797</v>
+      </c>
+      <c r="K10" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>2026</v>
-      </c>
-      <c r="B10" s="3">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3">
-        <v>21</v>
-      </c>
-      <c r="E10" s="3">
-        <v>46</v>
-      </c>
-      <c r="F10" s="3">
-        <v>32156</v>
-      </c>
-      <c r="G10" s="4">
-        <f t="shared" si="2"/>
-        <v>46131.906944444447</v>
-      </c>
-      <c r="H10" s="10">
-        <f t="shared" si="1"/>
-        <v>10.278349226391583</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17">
       <c r="A11" s="3">
         <v>2026</v>
       </c>
       <c r="B11" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" s="3">
         <v>21</v>
       </c>
-      <c r="E11" s="3">
-        <v>48</v>
-      </c>
-      <c r="F11" s="3">
-        <v>32223</v>
-      </c>
-      <c r="G11" s="4">
-        <f t="shared" si="2"/>
-        <v>46131.908333333333</v>
-      </c>
-      <c r="H11" s="10">
-        <f t="shared" si="1"/>
-        <v>2.1047534863937472</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E11" s="15">
+        <v>23</v>
+      </c>
+      <c r="F11" s="15">
+        <v>11</v>
+      </c>
+      <c r="H11" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I11" s="8">
+        <f>((H11-$L$3)/$L$2-G11)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="3">
         <v>2026</v>
       </c>
       <c r="B12" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12" s="3">
         <v>21</v>
       </c>
-      <c r="E12" s="3">
-        <v>50</v>
-      </c>
-      <c r="F12" s="3">
-        <v>32273</v>
-      </c>
-      <c r="G12" s="4">
-        <f t="shared" si="2"/>
-        <v>46131.909722222219</v>
-      </c>
-      <c r="H12" s="10">
-        <f t="shared" si="1"/>
-        <v>10.931157746395911</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E12" s="15">
+        <v>23</v>
+      </c>
+      <c r="F12" s="15">
+        <v>11</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I12" s="8">
+        <f>((H12-$L$3)/$L$2-G12)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="3">
         <v>2026</v>
       </c>
       <c r="B13" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3">
         <v>21</v>
       </c>
-      <c r="E13" s="3">
-        <v>52</v>
-      </c>
-      <c r="F13" s="3">
-        <v>32384</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" ref="G13" si="3">DATE(A13,B13,C13)+TIME(D13,E13,0)</f>
-        <v>46131.911111111112</v>
-      </c>
-      <c r="H13" s="10">
-        <f t="shared" si="1"/>
-        <v>-41.24243768542874</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E13" s="15">
+        <v>23</v>
+      </c>
+      <c r="F13" s="15">
+        <v>11</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I13" s="8">
+        <f>((H13-$L$3)/$L$2-G13)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="3">
         <v>2026</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" s="3">
         <v>21</v>
       </c>
-      <c r="E14" s="3">
-        <v>57</v>
-      </c>
-      <c r="F14" s="3">
-        <v>32487</v>
-      </c>
-      <c r="G14" s="4">
-        <f t="shared" ref="G14:G16" si="4">DATE(A14,B14,C14)+TIME(D14,E14,0)</f>
-        <v>46131.914583333331</v>
-      </c>
-      <c r="H14" s="10">
-        <f t="shared" si="1"/>
-        <v>2.823573118665081</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E14" s="15">
+        <v>23</v>
+      </c>
+      <c r="F14" s="15">
+        <v>11</v>
+      </c>
+      <c r="H14" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I14" s="8">
+        <f>((H14-$L$3)/$L$2-G14)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="3">
         <v>2026</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D15" s="3">
         <v>21</v>
       </c>
-      <c r="G15" s="4">
-        <f t="shared" si="4"/>
-        <v>46131.875</v>
-      </c>
-      <c r="H15" s="10">
-        <f t="shared" si="1"/>
-        <v>30813.271048472772</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E15" s="15">
+        <v>23</v>
+      </c>
+      <c r="F15" s="15">
+        <v>11</v>
+      </c>
+      <c r="H15" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I15" s="8">
+        <f>((H15-$L$3)/$L$2-G15)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="3">
         <v>2026</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" s="3">
         <v>21</v>
       </c>
-      <c r="G16" s="4">
-        <f t="shared" si="4"/>
-        <v>46131.875</v>
-      </c>
-      <c r="H16" s="10">
-        <f t="shared" si="1"/>
-        <v>30813.271048472772</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="E16" s="15">
+        <v>23</v>
+      </c>
+      <c r="F16" s="15">
+        <v>11</v>
+      </c>
+      <c r="H16" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I16" s="8">
+        <f>((H16-$L$3)/$L$2-G16)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>2026</v>
       </c>
       <c r="B17" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D17" s="3">
         <v>21</v>
       </c>
-      <c r="G17" s="4">
-        <f t="shared" ref="G17:G19" si="5">DATE(A17,B17,C17)+TIME(D17,E17,0)</f>
-        <v>46131.875</v>
-      </c>
-      <c r="H17" s="10">
-        <f t="shared" si="1"/>
-        <v>30813.271048472772</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="E17" s="15">
+        <v>23</v>
+      </c>
+      <c r="F17" s="15">
+        <v>11</v>
+      </c>
+      <c r="H17" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I17" s="8">
+        <f>((H17-$L$3)/$L$2-G17)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>2026</v>
       </c>
       <c r="B18" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18" s="3">
         <v>21</v>
       </c>
-      <c r="G18" s="4">
-        <f t="shared" si="5"/>
-        <v>46131.875</v>
-      </c>
-      <c r="H18" s="10">
-        <f t="shared" si="1"/>
-        <v>30813.271048472772</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="E18" s="15">
+        <v>23</v>
+      </c>
+      <c r="F18" s="15">
+        <v>11</v>
+      </c>
+      <c r="H18" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I18" s="8">
+        <f>((H18-$L$3)/$L$2-G18)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3">
         <v>2026</v>
       </c>
       <c r="B19" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" s="3">
         <v>21</v>
       </c>
-      <c r="G19" s="4">
-        <f t="shared" si="5"/>
-        <v>46131.875</v>
-      </c>
-      <c r="H19" s="10">
-        <f t="shared" si="1"/>
-        <v>30813.271048472772</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="E19" s="15">
+        <v>23</v>
+      </c>
+      <c r="F19" s="15">
+        <v>11</v>
+      </c>
+      <c r="H19" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I19" s="8">
+        <f>((H19-$L$3)/$L$2-G19)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="3">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3">
+        <v>17</v>
+      </c>
+      <c r="D20" s="3">
+        <v>21</v>
+      </c>
+      <c r="E20" s="15">
+        <v>23</v>
+      </c>
+      <c r="F20" s="15">
+        <v>11</v>
+      </c>
+      <c r="H20" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I20" s="8">
+        <f>((H20-$L$3)/$L$2-G20)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="3">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>17</v>
+      </c>
+      <c r="D21" s="3">
+        <v>21</v>
+      </c>
+      <c r="E21" s="15">
+        <v>23</v>
+      </c>
+      <c r="F21" s="15">
+        <v>11</v>
+      </c>
+      <c r="H21" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I21" s="8">
+        <f>((H21-$L$3)/$L$2-G21)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="3">
+        <v>6</v>
+      </c>
+      <c r="C22" s="3">
+        <v>17</v>
+      </c>
+      <c r="D22" s="3">
+        <v>21</v>
+      </c>
+      <c r="E22" s="15">
+        <v>23</v>
+      </c>
+      <c r="F22" s="15">
+        <v>11</v>
+      </c>
+      <c r="H22" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I22" s="8">
+        <f>((H22-$L$3)/$L$2-G22)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="3">
+        <v>6</v>
+      </c>
+      <c r="C23" s="3">
+        <v>17</v>
+      </c>
+      <c r="D23" s="3">
+        <v>21</v>
+      </c>
+      <c r="E23" s="15">
+        <v>23</v>
+      </c>
+      <c r="F23" s="15">
+        <v>11</v>
+      </c>
+      <c r="H23" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I23" s="8">
+        <f>((H23-$L$3)/$L$2-G23)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="3">
+        <v>6</v>
+      </c>
+      <c r="C24" s="3">
+        <v>17</v>
+      </c>
+      <c r="D24" s="3">
+        <v>21</v>
+      </c>
+      <c r="E24" s="15">
+        <v>23</v>
+      </c>
+      <c r="F24" s="15">
+        <v>11</v>
+      </c>
+      <c r="H24" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I24" s="8">
+        <f>((H24-$L$3)/$L$2-G24)</f>
+        <v>5.1227642409959797</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="3">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3">
+        <v>17</v>
+      </c>
+      <c r="D25" s="3">
+        <v>21</v>
+      </c>
+      <c r="E25" s="15">
+        <v>23</v>
+      </c>
+      <c r="F25" s="15">
+        <v>11</v>
+      </c>
+      <c r="H25" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I25" s="8">
+        <f>((H25-$L$3)/$L$2-G25)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="3">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3">
+        <v>17</v>
+      </c>
+      <c r="D26" s="3">
+        <v>21</v>
+      </c>
+      <c r="E26" s="15">
+        <v>23</v>
+      </c>
+      <c r="F26" s="15">
+        <v>11</v>
+      </c>
+      <c r="H26" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I26" s="8">
+        <f>((H26-$L$3)/$L$2-G26)</f>
+        <v>5.1227642409959797</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="3">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3">
+        <v>17</v>
+      </c>
+      <c r="D27" s="3">
+        <v>21</v>
+      </c>
+      <c r="E27" s="15">
+        <v>23</v>
+      </c>
+      <c r="F27" s="15">
+        <v>11</v>
+      </c>
+      <c r="H27" s="17">
+        <f t="shared" si="0"/>
+        <v>46190.891099537039</v>
+      </c>
+      <c r="I27" s="8">
+        <f>((H27-$L$3)/$L$2-G27)</f>
+        <v>5.1227642409959797</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1625,7 +1864,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H19">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1645,14 +1884,4 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B540D6-1361-40C7-BA95-F1466D26A402}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>